--- a/model_outputs_paper1/TASK_A_SCIM/SCIM_3class_shap_top10.xlsx
+++ b/model_outputs_paper1/TASK_A_SCIM/SCIM_3class_shap_top10.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.212794780731201</v>
+        <v>1.24681031703949</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3971017897129059</v>
+        <v>0.4514860212802887</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3847211599349976</v>
+        <v>0.4088045954704285</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.35160893201828</v>
+        <v>0.3591464757919312</v>
       </c>
     </row>
     <row r="6">
@@ -475,57 +475,57 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2894531488418579</v>
+        <v>0.302600622177124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>num__rehab_year_adm</t>
+          <t>num__SCIM_acute_to_rehab_gap</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.259339451789856</v>
+        <v>0.2760683596134186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>num__SCIM_acute_to_rehab_gap</t>
+          <t>num__acute_AS_SUB_adm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2543296217918396</v>
+        <v>0.2256175875663757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>num__acute_AS_SUB_adm</t>
+          <t>num__rehab_KF_SUB_adm</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2362809032201767</v>
+        <v>0.2170299142599106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>num__rehab_month_adm</t>
+          <t>num__acute_mobility_ratio</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2315347939729691</v>
+        <v>0.2069400250911713</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>num__rehab_KF_SUB_adm</t>
+          <t>num__age_at_entry</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2107975482940674</v>
+        <v>0.2026606351137161</v>
       </c>
     </row>
   </sheetData>
